--- a/Ferramenta de investimentos.xlsx
+++ b/Ferramenta de investimentos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30610"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD687D32-A7CA-4B0C-85B1-5078F2512E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2882D4A5-A926-4E16-AF02-24FE8062DB3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,6 +36,7 @@
     <definedName name="_xlchart.v1.7" hidden="1">Invst!$C$43:$C$46</definedName>
     <definedName name="_xlchart.v1.8" hidden="1">Invst!$D$42</definedName>
     <definedName name="_xlchart.v1.9" hidden="1">Invst!$D$43:$D$46</definedName>
+    <definedName name="opc">Invst!$D$24:$D$24</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -137,7 +138,7 @@
     <t>Perfil</t>
   </si>
   <si>
-    <t>Moderado</t>
+    <t>Conservador</t>
   </si>
   <si>
     <t>Valor a ser investido por mês</t>
@@ -176,7 +177,7 @@
     <t>%</t>
   </si>
   <si>
-    <t>Conservador</t>
+    <t>Moderado</t>
   </si>
   <si>
     <t>Agressivo</t>
@@ -6338,22 +6339,22 @@
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>0.32</c:v>
+                  <c:v>0.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.3</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.08</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -20200,11 +20201,11 @@
       </c>
       <c r="C28" s="32">
         <f>VLOOKUP($D$24&amp;"-"&amp;B28,aux!$A:$D,4,FALSE)</f>
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="D28" s="33">
         <f>$D$25*C28</f>
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -20213,11 +20214,11 @@
       </c>
       <c r="C29" s="32">
         <f>VLOOKUP($D$24&amp;"-"&amp;B29,aux!$A:$D,4,FALSE)</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D29" s="33">
         <f t="shared" ref="D29:D33" si="2">$D$25*C29</f>
-        <v>180</v>
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -20226,11 +20227,11 @@
       </c>
       <c r="C30" s="32">
         <f>VLOOKUP($D$24&amp;"-"&amp;B30,aux!$A:$D,4,FALSE)</f>
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="D30" s="33">
         <f t="shared" si="2"/>
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -20252,11 +20253,11 @@
       </c>
       <c r="C32" s="32">
         <f>VLOOKUP($D$24&amp;"-"&amp;B32,aux!$A:$D,4,FALSE)</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="33">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:4">
@@ -20265,11 +20266,11 @@
       </c>
       <c r="C33" s="32">
         <f>VLOOKUP($D$24&amp;"-"&amp;B33,aux!$A:$D,4,FALSE)</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="33">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:4">
@@ -20338,7 +20339,7 @@
         <v>Conservador-PAPEL</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C2" s="66" t="s">
         <v>24</v>
@@ -20353,7 +20354,7 @@
         <v>Conservador-TIJOLO</v>
       </c>
       <c r="B3" s="65" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C3" s="66" t="s">
         <v>25</v>
@@ -20368,7 +20369,7 @@
         <v>Conservador-HÏBRIDO</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C4" s="66" t="s">
         <v>26</v>
@@ -20383,7 +20384,7 @@
         <v>Conservador-FOFs</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C5" s="66" t="s">
         <v>27</v>
@@ -20398,7 +20399,7 @@
         <v>Conservador-DESENVOLVIMENTO</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C6" s="66" t="s">
         <v>28</v>
@@ -20413,7 +20414,7 @@
         <v>Conservador-HOTELARIAS</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C7" s="66" t="s">
         <v>29</v>
@@ -20428,7 +20429,7 @@
         <v>Moderado-PAPEL</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>24</v>
@@ -20443,7 +20444,7 @@
         <v>Moderado-TIJOLO</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C9" s="66" t="s">
         <v>25</v>
@@ -20458,7 +20459,7 @@
         <v>Moderado-HÏBRIDO</v>
       </c>
       <c r="B10" s="65" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C10" s="66" t="s">
         <v>26</v>
@@ -20473,7 +20474,7 @@
         <v>Moderado-FOFs</v>
       </c>
       <c r="B11" s="65" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C11" s="66" t="s">
         <v>27</v>
@@ -20488,7 +20489,7 @@
         <v>Moderado-DESENVOLVIMENTO</v>
       </c>
       <c r="B12" s="65" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C12" s="66" t="s">
         <v>28</v>
@@ -20503,7 +20504,7 @@
         <v>Moderado-HOTELARIAS</v>
       </c>
       <c r="B13" s="65" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C13" s="66" t="s">
         <v>29</v>
